--- a/Public goods list.xlsx
+++ b/Public goods list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suyeon\Desktop\NMNDL\00. 행정\회계\Slack-Goods Order Bot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suyeon\Desktop\NMNDL\00. 행정\회계\Slack\Slack-Goods Order Bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4134B81F-9250-4DEF-B586-AFF8CA3418F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2922CFD5-AF4F-4E2F-BE33-D9962142DEEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0A7FE512-1942-462E-97F4-E72AC556F825}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0A7FE512-1942-462E-97F4-E72AC556F825}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1147,7 +1147,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="2">
-        <v>203500</v>
+        <v>264000</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
